--- a/data/trans_bre/P38C-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P38C-Habitat-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 8,61</t>
+          <t>1,08; 9,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 11,23</t>
+          <t>2,47; 11,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 10,73</t>
+          <t>1,31; 11,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 13,83</t>
+          <t>2,81; 14,02</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 10,85</t>
+          <t>5,2; 10,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 53,17</t>
+          <t>5,45; 51,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,93; 13,51</t>
+          <t>6,2; 13,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,48; 164,05</t>
+          <t>6,89; 148,84</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 10,82</t>
+          <t>2,98; 10,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,26; 17,34</t>
+          <t>5,1; 17,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 13,95</t>
+          <t>3,65; 13,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 22,72</t>
+          <t>6,31; 23,85</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 7,36</t>
+          <t>0,59; 7,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 7,94</t>
+          <t>-15,68; 7,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 9,33</t>
+          <t>0,71; 9,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 10,08</t>
+          <t>-18,76; 10,1</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 7,79</t>
+          <t>4,23; 7,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 28,75</t>
+          <t>4,53; 30,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,19; 9,64</t>
+          <t>5,08; 9,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 51,8</t>
+          <t>5,62; 52,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P38C-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P38C-Habitat-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,43</t>
+          <t>5,96</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,09</t>
+          <t>0,67; 8,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 11,51</t>
+          <t>1,9; 10,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 11,33</t>
+          <t>0,83; 11,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 14,02</t>
+          <t>2,19; 12,3</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23,06</t>
+          <t>7,51</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 10,99</t>
+          <t>4,89; 11,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 51,48</t>
+          <t>3,97; 11,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,2; 13,73</t>
+          <t>5,94; 13,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,89; 148,84</t>
+          <t>5,0; 15,21</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10,36</t>
+          <t>7,79</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 10,66</t>
+          <t>3,09; 10,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 17,67</t>
+          <t>3,1; 13,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 13,85</t>
+          <t>3,84; 13,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 23,85</t>
+          <t>3,8; 17,51</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>7,16</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 7,47</t>
+          <t>0,23; 7,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 7,97</t>
+          <t>3,17; 10,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 9,62</t>
+          <t>0,24; 9,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 10,1</t>
+          <t>3,85; 14,23</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11,63</t>
+          <t>7,19</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,57</t>
+          <t>4,13; 7,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 30,02</t>
+          <t>5,14; 9,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 9,42</t>
+          <t>4,96; 9,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 52,69</t>
+          <t>6,35; 12,02</t>
         </is>
       </c>
     </row>
